--- a/importacoes/dados_colaboradores.xlsx
+++ b/importacoes/dados_colaboradores.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://arenabsbcombr-my.sharepoint.com/personal/joel_costa_arenabsb_com_br/Documents/Documentos/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-20.04\home\joelarena\sga\importacoes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E85B222B-A1A2-4AF3-BBE2-40FC7FCD61D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B192F8E5-6015-481B-927D-A326BB96436E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{A80E9AA9-EB43-465A-A44A-E5D1BAACFC5E}"/>
   </bookViews>
@@ -448,52 +448,51 @@
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.77734375" customWidth="1"/>
-    <col min="2" max="2" width="23.77734375" customWidth="1"/>
-    <col min="3" max="3" width="16.21875" customWidth="1"/>
-    <col min="4" max="4" width="22.21875" customWidth="1"/>
+    <col min="1" max="1" width="13.6640625" customWidth="1"/>
+    <col min="2" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
-        <v>11122233344</v>
+        <v>12345678000199</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="2">
+        <v>11122233344</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="2">
-        <v>12345678000199</v>
-      </c>
     </row>
-    <row r="3" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
-        <v>55566677788</v>
+        <v>98765432000111</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="2">
+        <v>55566677788</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="D3" s="2">
-        <v>98765432000111</v>
       </c>
     </row>
   </sheetData>
